--- a/stock_images_data.xlsx
+++ b/stock_images_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Local Image Path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sky Atmosphere, Blue Sky, Clouds,</t>
+          <t>Sky, Clouds, Blue Sky Atmosphere,</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -455,6 +460,11 @@
       <c r="D2" t="n">
         <v>55</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -464,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ornithology, Bird, Hummingbird</t>
+          <t>Hummingbird Ornithology, Bird,</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -473,6 +483,11 @@
       <c r="D3" t="n">
         <v>20</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -482,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sea, Rainbow, Rainfall, Subtropical</t>
+          <t>Rainbow, Rainfall, Subtropical Sea,</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -491,6 +506,11 @@
       <c r="D4" t="n">
         <v>106</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -500,7 +520,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Japan, Road, Sakura Cherry Blossoms,</t>
+          <t>Sakura Road, Cherry Japan, Blossoms,</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -509,6 +529,11 @@
       <c r="D5" t="n">
         <v>11</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_4.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -518,7 +543,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Flower, Marguerite, Cape Plant</t>
+          <t>Cape Marguerite, Plant Flower,</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -527,6 +552,11 @@
       <c r="D6" t="n">
         <v>15</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_5.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -536,7 +566,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rest Under Relaxing The Tree</t>
+          <t>Rest Tree The Under Relaxing</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -545,6 +575,11 @@
       <c r="D7" t="n">
         <v>108</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -554,7 +589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grass Rabbit, Wild Cottontail</t>
+          <t>Cottontail Wild Grass Rabbit,</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -563,6 +598,11 @@
       <c r="D8" t="n">
         <v>10</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_7.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -572,7 +612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Flowers, Crocus, Plant Spring,</t>
+          <t>Flowers, Spring, Plant Crocus,</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -581,6 +621,11 @@
       <c r="D9" t="n">
         <v>44</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_8.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -590,7 +635,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Café, Vacation, Drink, Coffee, Table</t>
+          <t>Drink, Coffee, Vacation, Café, Table</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -599,6 +644,11 @@
       <c r="D10" t="n">
         <v>5</v>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_9.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -608,7 +658,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waterfall, Light Epic, Nature, Fall,</t>
+          <t>Light Epic, Waterfall, Nature, Fall,</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -617,6 +667,11 @@
       <c r="D11" t="n">
         <v>21</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_10.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -626,7 +681,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Field, Morning, Nature Sunrise, Dawn,</t>
+          <t>Field, Morning, Sunrise, Nature Dawn,</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -635,6 +690,11 @@
       <c r="D12" t="n">
         <v>131</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_11.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -644,7 +704,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Birdwatching, Bird, Animal Robin,</t>
+          <t>Animal Birdwatching, Robin, Bird,</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -653,6 +713,11 @@
       <c r="D13" t="n">
         <v>19</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_12.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -662,7 +727,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Soil, Flowers, Seedlings, Spring Bloom</t>
+          <t>Soil, Seedlings, Flowers, Spring Bloom</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -671,6 +736,11 @@
       <c r="D14" t="n">
         <v>9</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_13.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -680,7 +750,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hills Highway, Countryside, Road,</t>
+          <t>Countryside, Road, Hills Highway,</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -689,6 +759,11 @@
       <c r="D15" t="n">
         <v>14</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_14.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -698,7 +773,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cityscape, Bridge, City Monochrome,</t>
+          <t>Bridge, Monochrome, Cityscape, City</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -707,6 +782,11 @@
       <c r="D16" t="n">
         <v>13</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_15.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -716,7 +796,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Water Sakura, Cherry Spring, Blossoms,</t>
+          <t>Spring, Cherry Sakura, Water Blossoms,</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -725,6 +805,11 @@
       <c r="D17" t="n">
         <v>12</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_16.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -734,7 +819,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Background, Easter, Template, Art Eggs,</t>
+          <t>Background, Easter, Eggs, Template, Art</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -743,6 +828,11 @@
       <c r="D18" t="n">
         <v>2</v>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_17.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -752,7 +842,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Indian Ornithology, Chat, Bird, Species</t>
+          <t>Species Ornithology, Indian Chat, Bird,</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -761,6 +851,11 @@
       <c r="D19" t="n">
         <v>53</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_18.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -770,7 +865,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Winter, Village, Town, Season Night,</t>
+          <t>Village, Season Town, Winter, Night,</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -779,6 +874,11 @@
       <c r="D20" t="n">
         <v>15</v>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_19.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -788,7 +888,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bloom Pansy, Viola, Blossom, Flower,</t>
+          <t>Blossom, Flower, Bloom Viola, Pansy,</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -797,6 +897,11 @@
       <c r="D21" t="n">
         <v>36</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_20.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -806,7 +911,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vacations Architecture, Port, Lake,</t>
+          <t>Port, Architecture, Lake, Vacations</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -815,6 +920,11 @@
       <c r="D22" t="n">
         <v>49</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_21.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -824,7 +934,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flowers, Plant Sunflowers,</t>
+          <t>Flowers, Sunflowers, Plant</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -833,6 +943,11 @@
       <c r="D23" t="n">
         <v>21</v>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_22.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -842,7 +957,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spring, Morning Flowers, Coffee,</t>
+          <t>Flowers, Morning Coffee, Spring,</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -851,6 +966,11 @@
       <c r="D24" t="n">
         <v>10</v>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_23.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -860,7 +980,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Peak, Wanaka, Mountains Lake, Roys</t>
+          <t>Lake, Wanaka, Roys Peak, Mountains</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -869,6 +989,11 @@
       <c r="D25" t="n">
         <v>19</v>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_24.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -878,7 +1003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thank for you many downloads likes. and everyone. you,</t>
+          <t>you likes. you, and everyone. Thank downloads for many</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -887,6 +1012,11 @@
       <c r="D26" t="n">
         <v>0</v>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_25.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -896,7 +1026,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Beach, Exploration Nature, Outdoors,</t>
+          <t>Nature, Outdoors, Exploration Beach,</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -905,6 +1035,11 @@
       <c r="D27" t="n">
         <v>150</v>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_26.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -914,7 +1049,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coast West Shot of Danish sunset. The Jutland. during</t>
+          <t>sunset. The Jutland. West during Danish of Coast Shot</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -923,6 +1058,11 @@
       <c r="D28" t="n">
         <v>11</v>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_27.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -932,7 +1072,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gentoo Animal Penguin, Bird,</t>
+          <t>Animal Gentoo Bird, Penguin,</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -941,6 +1081,11 @@
       <c r="D29" t="n">
         <v>22</v>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_28.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -950,7 +1095,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Water, Sea, Heaven, Beach, Tree Lantern,</t>
+          <t>Beach, Tree Sea, Heaven, Water, Lantern,</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -959,6 +1104,11 @@
       <c r="D30" t="n">
         <v>31</v>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_29.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -968,7 +1118,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spring, Easter, Bunny Easter</t>
+          <t>Bunny Spring, Easter Easter,</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -977,6 +1127,11 @@
       <c r="D31" t="n">
         <v>10</v>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_30.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -986,7 +1141,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>on green brown formation daytime rock during trees lake</t>
+          <t>formation daytime rock brown trees green during on lake</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -995,6 +1150,11 @@
       <c r="D32" t="n">
         <v>495</v>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_31.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1004,7 +1164,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Travel Tourist Attraction, Eiffel Tower,</t>
+          <t>Eiffel Tourist Attraction, Travel Tower,</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1013,6 +1173,11 @@
       <c r="D33" t="n">
         <v>21</v>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_32.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1022,7 +1187,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Standing Stones Stones, Clouds, Menhir,</t>
+          <t>Standing Clouds, Stones, Stones Menhir,</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1031,6 +1196,11 @@
       <c r="D34" t="n">
         <v>49</v>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_33.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1040,7 +1210,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Road, Winter, Trees, Frost, Path Snow,</t>
+          <t>Frost, Snow, Winter, Path Trees, Road,</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1049,6 +1219,11 @@
       <c r="D35" t="n">
         <v>24</v>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_34.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1058,7 +1233,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bird, Woodpecker</t>
+          <t>Woodpecker Bird,</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1067,6 +1242,11 @@
       <c r="D36" t="n">
         <v>20</v>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_35.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1076,7 +1256,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Classic Music, Tape, Cassette, Retro,</t>
+          <t>Cassette, Retro, Classic Tape, Music,</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1085,6 +1265,11 @@
       <c r="D37" t="n">
         <v>20</v>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_36.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1094,7 +1279,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Clouds, Energy, Power Wind Mills,</t>
+          <t>Power Clouds, Mills, Wind Energy,</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1103,6 +1288,11 @@
       <c r="D38" t="n">
         <v>101</v>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_37.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1112,7 +1302,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Piran Square, Tartini, Tourism, Travel,</t>
+          <t>Tourism, Travel, Square, Tartini, Piran</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1121,6 +1311,11 @@
       <c r="D39" t="n">
         <v>19</v>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_38.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1130,7 +1325,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eggs Colored Easter Nest, Eggs,</t>
+          <t>Easter Eggs, Eggs Nest, Colored</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1139,6 +1334,11 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_39.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1148,7 +1348,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Season, Winter, Nature, Travel Outdoors,</t>
+          <t>Season, Winter, Travel Nature, Outdoors,</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1157,6 +1357,11 @@
       <c r="D41" t="n">
         <v>24</v>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_40.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1166,7 +1371,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Melting Glaciers, Glacier Glacier, Dying</t>
+          <t>Glacier, Glacier Melting Glaciers, Dying</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1175,6 +1380,11 @@
       <c r="D42" t="n">
         <v>27</v>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_41.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1184,7 +1394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Forest, Nature Jungle, Tropical, Green,</t>
+          <t>Tropical, Green, Jungle, Nature Forest,</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1193,6 +1403,11 @@
       <c r="D43" t="n">
         <v>22</v>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_42.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1202,7 +1417,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bloom, Petals Blossom, Tulip, Flower,</t>
+          <t>Blossom, Petals Tulip, Flower, Bloom,</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1211,6 +1426,11 @@
       <c r="D44" t="n">
         <v>35</v>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_43.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1220,7 +1440,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Flowers, Petals Pink</t>
+          <t>Pink Flowers, Petals</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1229,6 +1449,11 @@
       <c r="D45" t="n">
         <v>0</v>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_44.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1238,7 +1463,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Passion Flower, Flower Passiflora,</t>
+          <t>Flower Passiflora, Passion Flower,</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1247,6 +1472,11 @@
       <c r="D46" t="n">
         <v>66</v>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_45.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1256,7 +1486,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Faith, Religion, Prayer, Hope, Blessing</t>
+          <t>Hope, Prayer, Blessing Faith, Religion,</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1265,6 +1495,11 @@
       <c r="D47" t="n">
         <v>57</v>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_46.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1274,7 +1509,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Space, Cosmos Universe, Galaxy, Star,</t>
+          <t>Space, Star, Cosmos Universe, Galaxy,</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1283,6 +1518,11 @@
       <c r="D48" t="n">
         <v>40</v>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_47.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1292,7 +1532,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Macro Insect, Nature, Dragonfly,</t>
+          <t>Macro Nature, Dragonfly, Insect,</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1300,6 +1540,2265 @@
       </c>
       <c r="D49" t="n">
         <v>3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_48.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/10/18/09/budapest-6928973__340.jpg</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Budapest, Church Architecture, Hungary,</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>107</v>
+      </c>
+      <c r="D50" t="n">
+        <v>21</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_49.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/16/11/27/trees-7072255__340.jpg</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Foliage, Trees, Leaves, Forest, Magic</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>66</v>
+      </c>
+      <c r="D51" t="n">
+        <v>18</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_50.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/11/07/59/hotel-6862159__340.jpg</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ärztin die Die Lehmann genauer liegt Dr. Erholung! war 1880! meinem Klausenbach. der einen Kolonie! Ort. Film Heike Aufenthalt erste Es tollen Das in Bridges Wie Adams Nordrach Klinik für als Makatsch Reha Hope gemacht bei wunderbarer mit gibt</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>94</v>
+      </c>
+      <c r="D52" t="n">
+        <v>14</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_51.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/22/16/50/landscape-6887936__340.jpg</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>summit are owned and which by crafts. (848m). trees site of for This near buildings. constructions the old The managed Hiei temple. a Hinoki useful temple Enryaku-ji In reconstruction tree is future, cypress, woods used very plantation Mt.</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>160</v>
+      </c>
+      <c r="D53" t="n">
+        <v>45</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_52.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/07/13/08/flowers-7117464__340.jpg</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Blossom, Growth, Flowers, Nature, Bloom</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>63</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_53.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/02/04/10/31/cow-6992475__340.jpg</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>babies) day! any My baby (or due ☺️ are</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>155</v>
+      </c>
+      <c r="D55" t="n">
+        <v>142</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_54.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/02/19/43/port-6910972__340.jpg</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ship, Port, Sweden, Sea Boat,</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>89</v>
+      </c>
+      <c r="D56" t="n">
+        <v>22</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_55.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/21/42/heron-7120365__340.jpg</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>elsewhere. stock selling - Photographed as the FORBIDS to or link on sites Here a 2021 Pixabay licence: license is https://pixabay.com/service/license/ 29, February images</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>34</v>
+      </c>
+      <c r="D57" t="n">
+        <v>51</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_56.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/11/01/13/58/leaf-6760484__340.jpg</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Season, Leaf, Nature, Autumn, Fall, Leaf</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>171</v>
+      </c>
+      <c r="D58" t="n">
+        <v>53</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_57.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/08/27/18/50/water-6579313__340.jpg</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Trolltunga, Water, Ringedalsvannet</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>202</v>
+      </c>
+      <c r="D59" t="n">
+        <v>45</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_58.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/01/18/17/cat-6838844__340.jpg</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Feline Pet, European Cat, Shorthair,</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>156</v>
+      </c>
+      <c r="D60" t="n">
+        <v>49</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_59.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/26/20/43/baboon-6969935__340.jpg</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gesture Baboon, Wildlife, Animal,</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>140</v>
+      </c>
+      <c r="D61" t="n">
+        <v>41</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_60.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/19/28/savoy-7124124__340.jpg</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Vegetables, Carrots Savoy, Cabbage,</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>28</v>
+      </c>
+      <c r="D62" t="n">
+        <v>20</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_61.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/16/04/08/koi-fish-7071556__480.jpg</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fish, Water, Koi Pond,</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>54</v>
+      </c>
+      <c r="D63" t="n">
+        <v>64</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_62.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/07/09/02/29/family-6398107__340.jpg</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Family Beach, People, Ocean, Family,</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>219</v>
+      </c>
+      <c r="D64" t="n">
+        <v>57</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_63.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/02/26/21/47/elephant-7036431__340.jpg</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Animals Baby Elephant,</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>104</v>
+      </c>
+      <c r="D65" t="n">
+        <v>35</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_64.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/19/28/savoy-7124124__340.jpg</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Vegetables, Carrots Savoy, Cabbage,</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>24</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_65.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/10/08/ranunculus-7123057__340.jpg</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>a description (optional) Add</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>25</v>
+      </c>
+      <c r="D67" t="n">
+        <v>15</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_66.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/17/33/great-cormorant-7119976__340.jpg</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Bird Great Cormorant,</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>36</v>
+      </c>
+      <c r="D68" t="n">
+        <v>24</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_67.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/19/07/flower-7124081__340.jpg</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Petals, Plant Flower, Daffodil,</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>21</v>
+      </c>
+      <c r="D69" t="n">
+        <v>14</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_68.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/28/18/46/sea-6975501__340.jpg</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sky, Clouds, Waves, Sea, Storm, Overcast</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>102</v>
+      </c>
+      <c r="D70" t="n">
+        <v>38</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_69.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2017/02/08/17/24/fantasy-2049567__340.jpg</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Butterflies, Mushrooms, Forest Fantasy,</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3322</v>
+      </c>
+      <c r="D71" t="n">
+        <v>536</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_70.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/15/15/19/child-7070570__340.jpg</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Flowers, Meadow, Kid Child, Boy, Cute,</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>43</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_71.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/12/18/grass-7115462__340.jpg</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Plants, Ear, Oats, Barley Grass,</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>46</v>
+      </c>
+      <c r="D73" t="n">
+        <v>44</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_72.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/10/14/13/50/book-6709160__340.jpg</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Reading, Book, Literature, Library</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>130</v>
+      </c>
+      <c r="D74" t="n">
+        <v>57</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_73.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/13/59/wood-anemones-7115637__340.jpg</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Buttercups Anemones, Anemone, Wood</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>46</v>
+      </c>
+      <c r="D75" t="n">
+        <v>39</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_74.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2017/12/15/13/51/polynesia-3021072__340.jpg</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>and beach daytime during red white on boat</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2610</v>
+      </c>
+      <c r="D76" t="n">
+        <v>499</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_75.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/03/09/30/flower-7108476__340.jpg</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bee, Pollination, Flower, Insect Bloom,</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>50</v>
+      </c>
+      <c r="D77" t="n">
+        <v>68</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_76.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/11/18/14/letter-box-7126374__480.jpg</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Office Letter Post Delivery, Email Box,</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>17</v>
+      </c>
+      <c r="D78" t="n">
+        <v>12</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_77.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/17/23/10/sunset-6945937__340.jpg</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sunset Lake At Calm</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>59</v>
+      </c>
+      <c r="D79" t="n">
+        <v>18</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_78.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/04/22/33/sunflowers-7112463__340.jpg</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>sunflowers Illustration, farming,</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>72</v>
+      </c>
+      <c r="D80" t="n">
+        <v>77</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_79.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/02/19/21/46/beach-7023446__340.jpg</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Beach, Sand, Sea, North Winter</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>30</v>
+      </c>
+      <c r="D81" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_80.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/13/16/37/trees-6935614__340.jpg</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Season, Winter, Trees, Nature, Outdoors</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>90</v>
+      </c>
+      <c r="D82" t="n">
+        <v>18</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_81.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/02/14/25/flower-7043267__340.jpg</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Blossom, Botany Flower, Rose, Bloom,</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>107</v>
+      </c>
+      <c r="D83" t="n">
+        <v>91</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_82.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/27/11/55/winter-6897046__340.jpg</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Macro Frost, Winter, Nature, Texture,</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>113</v>
+      </c>
+      <c r="D84" t="n">
+        <v>32</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_83.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/28/14/30/bird-6899457__340.jpg</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Blackbird, Ornithology, Species Bird,</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>109</v>
+      </c>
+      <c r="D85" t="n">
+        <v>27</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_84.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/14/27/trees-7123499__340.jpg</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Landscape Rural, Clouds, Trees, Nature,</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>14</v>
+      </c>
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_85.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/16/20/38/coffee-6943139__340.jpg</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Pencils, Office Eraser, Coffee,</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>69</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_86.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/07/18/04/00/lotus-6474572__340.jpg</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Lotus, Pink Flower, Lotus Flower</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>279</v>
+      </c>
+      <c r="D88" t="n">
+        <v>45</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_87.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/01/15/31/bus-7105041__340.jpg</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Es frei… sind noch Plätze</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>43</v>
+      </c>
+      <c r="D89" t="n">
+        <v>34</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_88.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/21/19/21/crocus-6955548__340.jpg</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Purple Plants, Crocus Flowers, Crocus,</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>77</v>
+      </c>
+      <c r="D90" t="n">
+        <v>16</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_89.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/11/09/18/birds-7125333__340.jpg</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022 March in 21, Taken</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>16</v>
+      </c>
+      <c r="D91" t="n">
+        <v>7</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_90.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/12/22/48/mountain-6867146__340.jpg</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Clouds Winter, Mountain, Summit, Forest,</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>82</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_91.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/07/33/ice-cream-cone-7122797__340.jpg</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ice Cone, Flower Cream Squirrel,</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>16</v>
+      </c>
+      <c r="D93" t="n">
+        <v>11</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_92.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/09/29/flower-7121113__480.jpg</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Magnolia, Tree, Flower, Spring Flowers</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_93.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/09/46/flowers-7115215__340.jpg</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Garden Flowers, Bouquet,</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>47</v>
+      </c>
+      <c r="D95" t="n">
+        <v>26</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_94.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/04/09/02/winter-7046891__340.jpg</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Stop the Ukraine! Help war!</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>56</v>
+      </c>
+      <c r="D96" t="n">
+        <v>15</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_95.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/03/08/33/jay-7108357__340.jpg</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Animal, Snow, Jay, Bird, Winter</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>62</v>
+      </c>
+      <c r="D97" t="n">
+        <v>48</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_96.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/07/14/dungeon-7120925__340.jpg</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>a the Augustins, (France) museum. former in Augustinian become 1300-1400, has convent Toulouse French) (Les Built</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>17</v>
+      </c>
+      <c r="D98" t="n">
+        <v>11</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_97.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/11/09/16/birds-7125327__340.jpg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Goslings, Egyptian Waterfowl Birds,</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>15</v>
+      </c>
+      <c r="D99" t="n">
+        <v>8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_98.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/08/16/peach-blossom-7115083__340.jpg</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Blossom, Tree Flowers, Peach Branch,</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>41</v>
+      </c>
+      <c r="D100" t="n">
+        <v>58</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_99.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/01/15/32/happy-new-year-6838276__340.jpg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Year Year, Regards, 2022, New Happy</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>45</v>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_100.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/03/17/48/flowers-7109567__340.jpg</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Flowers, Quince Botany,</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>55</v>
+      </c>
+      <c r="D102" t="n">
+        <v>47</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_101.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2016/11/29/05/45/astronomy-1867616__340.jpg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Astronomy, Bright, Constellation, Dark</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2989</v>
+      </c>
+      <c r="D103" t="n">
+        <v>484</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_102.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/02/14/10/35/flowers-7012876__340.jpg</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Blossom, Flowers, Nature Botany, Bloom,</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>43</v>
+      </c>
+      <c r="D104" t="n">
+        <v>13</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_103.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/08/23/08/28/path-6567149__340.jpg</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Rural, Road, Path, Nature, Countryside</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>178</v>
+      </c>
+      <c r="D105" t="n">
+        <v>36</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_104.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/02/14/06/54/bird-7012586__340.jpg</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ibis, Spiny Ornithology Bird,</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>141</v>
+      </c>
+      <c r="D106" t="n">
+        <v>102</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_105.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/08/27/10/16/baby-6578335__340.jpg</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Portrait, Daughter Child, Baby, Girl,</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>179</v>
+      </c>
+      <c r="D107" t="n">
+        <v>54</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_106.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/20/15/01/christmas-tree-6883263__340.jpg</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tree, Christmas Ornaments,</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>147</v>
+      </c>
+      <c r="D108" t="n">
+        <v>99</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_107.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/09/30/18/10/sunrise-6670717__340.jpg</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Jura Fog, Sunrise, Mountains, Swabian</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>140</v>
+      </c>
+      <c r="D109" t="n">
+        <v>27</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_108.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/05/22/54/giant-lily-7114496__480.jpg</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>dies... and life stirbt… Dorianthes und Leben her once einmal 3 Palmeri. flower hoch. ihre erste meters high. Blüht in Meter nach Makes Macht nur Blooms Jahren. ***************************** years. Blume ihrem first 40 at only</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>47</v>
+      </c>
+      <c r="D110" t="n">
+        <v>32</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_109.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/22/27/postcard-7116453__340.jpg</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Card, Peacocks, Greeting Birds Postcard,</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>31</v>
+      </c>
+      <c r="D111" t="n">
+        <v>36</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_110.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/25/04/42/bird-6965228__340.jpg</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Great Species Ornithology, Egret, Bird,</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>89</v>
+      </c>
+      <c r="D112" t="n">
+        <v>47</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_111.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/10/16/30/flowers-6928749__340.jpg</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Beach, Sea Flowers, Cliff, Coast, Grass,</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>79</v>
+      </c>
+      <c r="D113" t="n">
+        <v>12</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_112.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/18/17/11/flower-6879399__340.jpg</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Dandelion, Wildflower, Seeds Flower,</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>88</v>
+      </c>
+      <c r="D114" t="n">
+        <v>14</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_113.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/14/20/21/book-6871220__340.jpg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Stop, Man, Paper Shades, Book, Page,</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>80</v>
+      </c>
+      <c r="D115" t="n">
+        <v>49</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_114.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/08/23/07/38/castle-6566978__340.jpg</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Monument, Building Park, Castle,</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>159</v>
+      </c>
+      <c r="D116" t="n">
+        <v>27</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_115.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/05/15/11/birds-7113827__340.jpg</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Greylag Goose, Ornithology Birds,</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>41</v>
+      </c>
+      <c r="D117" t="n">
+        <v>28</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_116.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/19/05/hyacinth-7120098__340.jpg</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Flowers, Nature Hyacinth, Spring,</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>15</v>
+      </c>
+      <c r="D118" t="n">
+        <v>9</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_117.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/05/00/25/bokeh-7112555__340.jpg</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Light, Bokeh, Background, Pattern, Art</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>27</v>
+      </c>
+      <c r="D119" t="n">
+        <v>27</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_118.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/02/10/53/easter-7106722__340.jpg</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Decoration Easter Bunny, Easter,</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>55</v>
+      </c>
+      <c r="D120" t="n">
+        <v>87</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_119.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/11/26/17/26/desert-6826299__340.jpg</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Dubai, Sand, Desert, Native Dunes,</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>48</v>
+      </c>
+      <c r="D121" t="n">
+        <v>14</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_120.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/03/09/04/pforphoto-7108433__340.jpg</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Piano… The</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>35</v>
+      </c>
+      <c r="D122" t="n">
+        <v>25</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_121.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2020/04/25/12/14/tech-5090539__340.jpg</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tech, Abstract Circle, Technology,</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>404</v>
+      </c>
+      <c r="D123" t="n">
+        <v>109</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_122.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/09/46/flowers-7115217__340.jpg</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Garden Flowers, Hyacinth,</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>40</v>
+      </c>
+      <c r="D124" t="n">
+        <v>28</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_123.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/28/05/17/cherry-blossoms-7096607__340.jpg</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pink Flowers, Sakura Cherry Blossoms,</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>61</v>
+      </c>
+      <c r="D125" t="n">
+        <v>24</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_124.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/12/12/coffee-7119373__480.jpg</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Dirty Coffee Stain, Coffee, Template,</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>26</v>
+      </c>
+      <c r="D126" t="n">
+        <v>19</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_125.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/02/02/13/50/happy-easter-6988491__340.jpg</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Spring, Decoration, Easter, Happy Theme</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>29</v>
+      </c>
+      <c r="D127" t="n">
+        <v>10</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_126.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/12/01/15/lotus-6863937__340.jpg</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Lotus, Flowers, Pads Pond, Lily</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>101</v>
+      </c>
+      <c r="D128" t="n">
+        <v>23</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_127.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/21/07/21/ring-tailed-lemur-6954076__340.jpg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ring Tailed Group, Lemur, Cub</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>160</v>
+      </c>
+      <c r="D129" t="n">
+        <v>115</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_128.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/07/04/03/bird-7116757__340.jpg</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>sudeste introducido es passeriforme Sturnidae reproduce estornino y hoy familia unos en hace Aires. Provincia común, vulgaris)​ una fue Argentina nativa o ave abundantemente especie se En de años (Sturnus pinto, la Buenos el del Paleártico. El</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>23</v>
+      </c>
+      <c r="D130" t="n">
+        <v>19</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_129.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/10/11/09/04/nature-6699893__340.jpg</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Spruce, Nature, Evergreen, Branches</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>99</v>
+      </c>
+      <c r="D131" t="n">
+        <v>21</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_130.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/07/22/tablets-7118912__340.jpg</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Drugs, Powder Tablets,</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>22</v>
+      </c>
+      <c r="D132" t="n">
+        <v>16</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_131.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/01/17/08/27/white-flowers-6944139__340.jpg</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Flowers, White Nature</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>49</v>
+      </c>
+      <c r="D133" t="n">
+        <v>11</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_132.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/09/14/14/46/cologne-6624212__340.jpg</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Cathedral, Night, Bridge, River Cologne,</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>98</v>
+      </c>
+      <c r="D134" t="n">
+        <v>27</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_133.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2015/12/01/20/28/road-1072823__340.jpg</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Season Road, Autumn, Fall, Forest,</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>5214</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1126</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_134.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/06/13/bird-7118767__340.jpg</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Geese, Fauna Species, Ornithology, Bird,</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>23</v>
+      </c>
+      <c r="D136" t="n">
+        <v>15</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_135.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/04/15/16/flowers-7111580__340.jpg</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ende 2022 Foto von März</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>27</v>
+      </c>
+      <c r="D137" t="n">
+        <v>20</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_136.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/10/10/20/33/mehtab-bagh-6698669__340.jpg</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Taj Bagh, India, Temple Mahal, Mehtab</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>73</v>
+      </c>
+      <c r="D138" t="n">
+        <v>15</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_137.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/05/35/tulips-7120798__340.jpg</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Tulips, Flora Plant, Flower,</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>10</v>
+      </c>
+      <c r="D139" t="n">
+        <v>4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_138.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/04/06/59/canada-goose-7110494__340.jpg</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Swim, Bird Canada Goose, Water</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>57</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_139.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/02/19/27/earth-7043847__340.jpg</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Earth, Planet, Homeland, Mankind</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>36</v>
+      </c>
+      <c r="D141" t="n">
+        <v>8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_140.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/07/04/04/starling-7116759__480.jpg</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>sudeste introducido es passeriforme Sturnidae reproduce estornino y hoy familia unos en hace Aires. Provincia común, vulgaris)​ una fue Argentina nativa o ave abundantemente especie se En de años (Sturnus pinto, la Buenos el del Paleártico. El</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>22</v>
+      </c>
+      <c r="D142" t="n">
+        <v>17</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_141.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/28/20/47/house-7098314__340.jpg</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Composition, view lake</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>81</v>
+      </c>
+      <c r="D143" t="n">
+        <v>81</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_142.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/17/33/bird-7119983__340.jpg</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Songbird, Blackbird, Animal Fauna, Bird,</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>18</v>
+      </c>
+      <c r="D144" t="n">
+        <v>11</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_143.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/10/04/bird-7123044__340.jpg</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>riverbanks. and bird, regions it cover to areas, farmlands, parks, inhabiting a Durian in residential In Redstart. wintering Japan, without low mountain snow is flat winter</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>10</v>
+      </c>
+      <c r="D145" t="n">
+        <v>6</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_144.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/11/09/07/29/newborn-6780840__340.jpg</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Newborn, Sleeping Baby, Costume,</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>91</v>
+      </c>
+      <c r="D146" t="n">
+        <v>21</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_145.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/02/20/46/cat-7107728__340.jpg</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Backyard, Kitten Cat, Outdoors, Grass,</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>54</v>
+      </c>
+      <c r="D147" t="n">
+        <v>36</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_146.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/stock_images_data.xlsx
+++ b/stock_images_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sky, Clouds, Blue Sky Atmosphere,</t>
+          <t>Sky, Sky Clouds, Blue Atmosphere,</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rainbow, Rainfall, Subtropical Sea,</t>
+          <t>Subtropical Rainbow, Sea, Rainfall,</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -520,7 +520,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sakura Road, Cherry Japan, Blossoms,</t>
+          <t>Cherry Blossoms, Japan, Road, Sakura</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cape Marguerite, Plant Flower,</t>
+          <t>Marguerite, Flower, Cape Plant</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rest Tree The Under Relaxing</t>
+          <t>Under The Relaxing Tree Rest</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cottontail Wild Grass Rabbit,</t>
+          <t>Cottontail Grass Rabbit, Wild</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -612,7 +612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Flowers, Spring, Plant Crocus,</t>
+          <t>Crocus, Flowers, Spring, Plant</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Drink, Coffee, Vacation, Café, Table</t>
+          <t>Table Vacation, Coffee, Drink, Café,</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Field, Morning, Sunrise, Nature Dawn,</t>
+          <t>Field, Morning, Sunrise, Dawn, Nature</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Animal Birdwatching, Robin, Bird,</t>
+          <t>Birdwatching, Animal Bird, Robin,</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Soil, Seedlings, Flowers, Spring Bloom</t>
+          <t>Seedlings, Soil, Spring Bloom Flowers,</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Countryside, Road, Hills Highway,</t>
+          <t>Road, Hills Highway, Countryside,</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spring, Cherry Sakura, Water Blossoms,</t>
+          <t>Water Sakura, Cherry Blossoms, Spring,</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Background, Easter, Eggs, Template, Art</t>
+          <t>Easter, Template, Background, Eggs, Art</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Species Ornithology, Indian Chat, Bird,</t>
+          <t>Species Bird, Ornithology, Chat, Indian</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Village, Season Town, Winter, Night,</t>
+          <t>Season Night, Village, Winter, Town,</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blossom, Flower, Bloom Viola, Pansy,</t>
+          <t>Pansy, Viola, Blossom, Bloom Flower,</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Port, Architecture, Lake, Vacations</t>
+          <t>Lake, Port, Vacations Architecture,</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flowers, Sunflowers, Plant</t>
+          <t>Sunflowers, Flowers, Plant</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Flowers, Morning Coffee, Spring,</t>
+          <t>Coffee, Spring, Flowers, Morning</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lake, Wanaka, Roys Peak, Mountains</t>
+          <t>Lake, Roys Mountains Peak, Wanaka,</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>you likes. you, and everyone. Thank downloads for many</t>
+          <t>you, everyone. likes. and many Thank you for downloads</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nature, Outdoors, Exploration Beach,</t>
+          <t>Exploration Beach, Nature, Outdoors,</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sunset. The Jutland. West during Danish of Coast Shot</t>
+          <t>sunset. during Shot of The Coast West Jutland. Danish</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Animal Gentoo Bird, Penguin,</t>
+          <t>Animal Penguin, Bird, Gentoo</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Beach, Tree Sea, Heaven, Water, Lantern,</t>
+          <t>Lantern, Heaven, Tree Sea, Beach, Water,</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bunny Spring, Easter Easter,</t>
+          <t>Bunny Easter, Spring, Easter</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>formation daytime rock brown trees green during on lake</t>
+          <t>green during formation rock lake daytime on trees brown</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eiffel Tourist Attraction, Travel Tower,</t>
+          <t>Attraction, Eiffel Travel Tower, Tourist</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Standing Clouds, Stones, Stones Menhir,</t>
+          <t>Standing Menhir, Stones Stones, Clouds,</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Frost, Snow, Winter, Path Trees, Road,</t>
+          <t>Path Trees, Winter, Road, Frost, Snow,</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cassette, Retro, Classic Tape, Music,</t>
+          <t>Classic Music, Retro, Cassette, Tape,</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Power Clouds, Mills, Wind Energy,</t>
+          <t>Energy, Wind Clouds, Power Mills,</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tourism, Travel, Square, Tartini, Piran</t>
+          <t>Square, Tartini, Tourism, Travel, Piran</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Easter Eggs, Eggs Nest, Colored</t>
+          <t>Easter Eggs Colored Nest, Eggs,</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Season, Winter, Travel Nature, Outdoors,</t>
+          <t>Season, Outdoors, Travel Winter, Nature,</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Glacier, Glacier Melting Glaciers, Dying</t>
+          <t>Melting Glaciers, Glacier, Glacier Dying</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tropical, Green, Jungle, Nature Forest,</t>
+          <t>Green, Forest, Jungle, Tropical, Nature</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blossom, Petals Tulip, Flower, Bloom,</t>
+          <t>Blossom, Tulip, Flower, Petals Bloom,</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pink Flowers, Petals</t>
+          <t>Flowers, Pink Petals</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Flower Passiflora, Passion Flower,</t>
+          <t>Flower, Passion Flower Passiflora,</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hope, Prayer, Blessing Faith, Religion,</t>
+          <t>Blessing Hope, Faith, Prayer, Religion,</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Space, Star, Cosmos Universe, Galaxy,</t>
+          <t>Galaxy, Space, Cosmos Star, Universe,</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Macro Nature, Dragonfly, Insect,</t>
+          <t>Macro Nature, Insect, Dragonfly,</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Budapest, Church Architecture, Hungary,</t>
+          <t>Hungary, Budapest, Church Architecture,</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Foliage, Trees, Leaves, Forest, Magic</t>
+          <t>Forest, Leaves, Trees, Magic Foliage,</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ärztin die Die Lehmann genauer liegt Dr. Erholung! war 1880! meinem Klausenbach. der einen Kolonie! Ort. Film Heike Aufenthalt erste Es tollen Das in Bridges Wie Adams Nordrach Klinik für als Makatsch Reha Hope gemacht bei wunderbarer mit gibt</t>
+          <t>wunderbarer Film Heike Makatsch gemacht erste Es mit als bei Die für 1880! Aufenthalt Kolonie! gibt der Klinik Nordrach Wie Reha in die Dr. Adams Klausenbach. meinem Das Bridges Ärztin war Ort. tollen liegt Erholung! einen genauer Lehmann Hope</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>summit are owned and which by crafts. (848m). trees site of for This near buildings. constructions the old The managed Hiei temple. a Hinoki useful temple Enryaku-ji In reconstruction tree is future, cypress, woods used very plantation Mt.</t>
+          <t>the Enryaku-ji are This woods summit tree temple buildings. is future, managed Mt. very plantation In (848m). by useful crafts. owned reconstruction constructions used temple. of Hiei for a near trees old which and cypress, The Hinoki site</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blossom, Growth, Flowers, Nature, Bloom</t>
+          <t>Growth, Blossom, Bloom Flowers, Nature,</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>babies) day! any My baby (or due ☺️ are</t>
+          <t>babies) due any (or ☺️ My baby day! are</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ship, Port, Sweden, Sea Boat,</t>
+          <t>Boat, Ship, Sea Sweden, Port,</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>elsewhere. stock selling - Photographed as the FORBIDS to or link on sites Here a 2021 Pixabay licence: license is https://pixabay.com/service/license/ 29, February images</t>
+          <t>the Here Pixabay Photographed FORBIDS is link https://pixabay.com/service/license/ licence: stock license selling 29, elsewhere. sites on or to 2021 a images as - February</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Season, Leaf, Nature, Autumn, Fall, Leaf</t>
+          <t>Season, Autumn, Nature, Leaf Fall, Leaf,</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trolltunga, Water, Ringedalsvannet</t>
+          <t>Water, Ringedalsvannet Trolltunga,</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Feline Pet, European Cat, Shorthair,</t>
+          <t>Feline Pet, Cat, European Shorthair,</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gesture Baboon, Wildlife, Animal,</t>
+          <t>Animal, Gesture Baboon, Wildlife,</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vegetables, Carrots Savoy, Cabbage,</t>
+          <t>Savoy, Cabbage, Vegetables, Carrots</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fish, Water, Koi Pond,</t>
+          <t>Pond, Water, Fish, Koi</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Family Beach, People, Ocean, Family,</t>
+          <t>Family, Family People, Ocean, Beach,</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Animals Baby Elephant,</t>
+          <t>Animals Elephant, Baby</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vegetables, Carrots Savoy, Cabbage,</t>
+          <t>Savoy, Cabbage, Vegetables, Carrots</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>a description (optional) Add</t>
+          <t>description a (optional) Add</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bird Great Cormorant,</t>
+          <t>Great Cormorant, Bird</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Petals, Plant Flower, Daffodil,</t>
+          <t>Flower, Daffodil, Petals, Plant</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sky, Clouds, Waves, Sea, Storm, Overcast</t>
+          <t>Sky, Overcast Clouds, Sea, Waves, Storm,</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Butterflies, Mushrooms, Forest Fantasy,</t>
+          <t>Butterflies, Forest Mushrooms, Fantasy,</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flowers, Meadow, Kid Child, Boy, Cute,</t>
+          <t>Child, Kid Cute, Boy, Meadow, Flowers,</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Plants, Ear, Oats, Barley Grass,</t>
+          <t>Grass, Barley Oats, Ear, Plants,</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Reading, Book, Literature, Library</t>
+          <t>Reading, Literature, Library Book,</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Buttercups Anemones, Anemone, Wood</t>
+          <t>Wood Anemones, Anemone, Buttercups</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>and beach daytime during red white on boat</t>
+          <t>and during white red boat daytime on beach</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Office Letter Post Delivery, Email Box,</t>
+          <t>Delivery, Email Box, Post Office Letter</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sunset Lake At Calm</t>
+          <t>At Sunset Calm Lake</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>sunflowers Illustration, farming,</t>
+          <t>sunflowers farming, Illustration,</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Beach, Sand, Sea, North Winter</t>
+          <t>Sand, Winter North Sea, Beach,</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Season, Winter, Trees, Nature, Outdoors</t>
+          <t>Season, Trees, Winter, Nature, Outdoors</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blossom, Botany Flower, Rose, Bloom,</t>
+          <t>Rose, Botany Blossom, Flower, Bloom,</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Macro Frost, Winter, Nature, Texture,</t>
+          <t>Texture, Winter, Frost, Nature, Macro</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackbird, Ornithology, Species Bird,</t>
+          <t>Species Blackbird, Bird, Ornithology,</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Landscape Rural, Clouds, Trees, Nature,</t>
+          <t>Rural, Landscape Trees, Clouds, Nature,</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pencils, Office Eraser, Coffee,</t>
+          <t>Eraser, Office Coffee, Pencils,</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lotus, Pink Flower, Lotus Flower</t>
+          <t>Pink Flower Lotus Lotus, Flower,</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Es frei… sind noch Plätze</t>
+          <t>Plätze frei… noch sind Es</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Purple Plants, Crocus Flowers, Crocus,</t>
+          <t>Crocus Purple Crocus, Flowers, Plants,</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2022 March in 21, Taken</t>
+          <t>March Taken 2022 21, in</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Clouds Winter, Mountain, Summit, Forest,</t>
+          <t>Mountain, Forest, Clouds Winter, Summit,</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ice Cone, Flower Cream Squirrel,</t>
+          <t>Cone, Cream Flower Ice Squirrel,</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Magnolia, Tree, Flower, Spring Flowers</t>
+          <t>Tree, Spring Magnolia, Flowers Flower,</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Garden Flowers, Bouquet,</t>
+          <t>Flowers, Bouquet, Garden</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Stop the Ukraine! Help war!</t>
+          <t>the Stop Ukraine! war! Help</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Animal, Snow, Jay, Bird, Winter</t>
+          <t>Jay, Bird, Winter Animal, Snow,</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>a the Augustins, (France) museum. former in Augustinian become 1300-1400, has convent Toulouse French) (Les Built</t>
+          <t>the (Les Augustinian has museum. French) Toulouse become 1300-1400, former (France) convent a Built Augustins, in</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Goslings, Egyptian Waterfowl Birds,</t>
+          <t>Birds, Egyptian Goslings, Waterfowl</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Blossom, Tree Flowers, Peach Branch,</t>
+          <t>Branch, Blossom, Flowers, Tree Peach</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Year Year, Regards, 2022, New Happy</t>
+          <t>New Year Happy Year, 2022, Regards,</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Flowers, Quince Botany,</t>
+          <t>Quince Flowers, Botany,</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Astronomy, Bright, Constellation, Dark</t>
+          <t>Constellation, Astronomy, Dark Bright,</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Blossom, Flowers, Nature Botany, Bloom,</t>
+          <t>Botany, Bloom, Blossom, Flowers, Nature</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rural, Road, Path, Nature, Countryside</t>
+          <t>Countryside Rural, Road, Nature, Path,</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ibis, Spiny Ornithology Bird,</t>
+          <t>Ibis, Spiny Bird, Ornithology</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Portrait, Daughter Child, Baby, Girl,</t>
+          <t>Child, Baby, Portrait, Daughter Girl,</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tree, Christmas Ornaments,</t>
+          <t>Christmas Ornaments, Tree,</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jura Fog, Sunrise, Mountains, Swabian</t>
+          <t>Swabian Mountains, Fog, Sunrise, Jura</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>dies... and life stirbt… Dorianthes und Leben her once einmal 3 Palmeri. flower hoch. ihre erste meters high. Blüht in Meter nach Makes Macht nur Blooms Jahren. ***************************** years. Blume ihrem first 40 at only</t>
+          <t>at ***************************** Palmeri. Dorianthes only high. erste Blooms meters her Jahren. dies... 3 und flower nur einmal ihrem Makes nach Leben in 40 Macht Blüht first ihre and hoch. Meter life years. once stirbt… Blume</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Card, Peacocks, Greeting Birds Postcard,</t>
+          <t>Birds Greeting Peacocks, Postcard, Card,</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Great Species Ornithology, Egret, Bird,</t>
+          <t>Species Bird, Egret, Ornithology, Great</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Beach, Sea Flowers, Cliff, Coast, Grass,</t>
+          <t>Grass, Beach, Cliff, Coast, Sea Flowers,</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Dandelion, Wildflower, Seeds Flower,</t>
+          <t>Flower, Wildflower, Dandelion, Seeds</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Stop, Man, Paper Shades, Book, Page,</t>
+          <t>Man, Paper Book, Shades, Page, Stop,</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Monument, Building Park, Castle,</t>
+          <t>Building Monument, Park, Castle,</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Greylag Goose, Ornithology Birds,</t>
+          <t>Birds, Greylag Ornithology Goose,</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Flowers, Nature Hyacinth, Spring,</t>
+          <t>Flowers, Spring, Hyacinth, Nature</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Light, Bokeh, Background, Pattern, Art</t>
+          <t>Pattern, Light, Bokeh, Background, Art</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Decoration Easter Bunny, Easter,</t>
+          <t>Easter, Easter Bunny, Decoration</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dubai, Sand, Desert, Native Dunes,</t>
+          <t>Sand, Dunes, Dubai, Desert, Native</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Piano… The</t>
+          <t>The Piano…</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tech, Abstract Circle, Technology,</t>
+          <t>Abstract Tech, Technology, Circle,</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Garden Flowers, Hyacinth,</t>
+          <t>Flowers, Hyacinth, Garden</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pink Flowers, Sakura Cherry Blossoms,</t>
+          <t>Pink Cherry Blossoms, Sakura Flowers,</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dirty Coffee Stain, Coffee, Template,</t>
+          <t>Coffee Template, Coffee, Stain, Dirty</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Spring, Decoration, Easter, Happy Theme</t>
+          <t>Happy Easter, Theme Spring, Decoration,</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lotus, Flowers, Pads Pond, Lily</t>
+          <t>Pond, Lily Pads Flowers, Lotus,</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ring Tailed Group, Lemur, Cub</t>
+          <t>Tailed Lemur, Ring Cub Group,</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>sudeste introducido es passeriforme Sturnidae reproduce estornino y hoy familia unos en hace Aires. Provincia común, vulgaris)​ una fue Argentina nativa o ave abundantemente especie se En de años (Sturnus pinto, la Buenos el del Paleártico. El</t>
+          <t>fue Argentina Aires. passeriforme del Buenos hoy y estornino ave El hace Provincia años es especie pinto, (Sturnus una abundantemente nativa Sturnidae la vulgaris)​ de reproduce el o familia se común, Paleártico. unos introducido sudeste en En</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Spruce, Nature, Evergreen, Branches</t>
+          <t>Branches Spruce, Nature, Evergreen,</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Drugs, Powder Tablets,</t>
+          <t>Powder Tablets, Drugs,</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cathedral, Night, Bridge, River Cologne,</t>
+          <t>River Bridge, Cologne, Night, Cathedral,</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Season Road, Autumn, Fall, Forest,</t>
+          <t>Forest, Season Autumn, Road, Fall,</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Geese, Fauna Species, Ornithology, Bird,</t>
+          <t>Bird, Geese, Fauna Ornithology, Species,</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ende 2022 Foto von März</t>
+          <t>von März Foto 2022 Ende</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Taj Bagh, India, Temple Mahal, Mehtab</t>
+          <t>Taj India, Mahal, Mehtab Bagh, Temple</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Tulips, Flora Plant, Flower,</t>
+          <t>Tulips, Plant, Flora Flower,</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Swim, Bird Canada Goose, Water</t>
+          <t>Bird Water Goose, Swim, Canada</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Earth, Planet, Homeland, Mankind</t>
+          <t>Mankind Homeland, Earth, Planet,</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>sudeste introducido es passeriforme Sturnidae reproduce estornino y hoy familia unos en hace Aires. Provincia común, vulgaris)​ una fue Argentina nativa o ave abundantemente especie se En de años (Sturnus pinto, la Buenos el del Paleártico. El</t>
+          <t>fue Argentina Aires. passeriforme del Buenos hoy y estornino ave El hace Provincia años es especie pinto, (Sturnus una abundantemente nativa Sturnidae la vulgaris)​ de reproduce el o familia se común, Paleártico. unos introducido sudeste en En</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Composition, view lake</t>
+          <t>view Composition, lake</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Songbird, Blackbird, Animal Fauna, Bird,</t>
+          <t>Animal Bird, Fauna, Songbird, Blackbird,</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>riverbanks. and bird, regions it cover to areas, farmlands, parks, inhabiting a Durian in residential In Redstart. wintering Japan, without low mountain snow is flat winter</t>
+          <t>cover Redstart. areas, Durian it is regions without In bird, flat in to inhabiting snow winter a riverbanks. and residential low mountain Japan, farmlands, wintering parks,</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Newborn, Sleeping Baby, Costume,</t>
+          <t>Sleeping Costume, Newborn, Baby,</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Backyard, Kitten Cat, Outdoors, Grass,</t>
+          <t>Grass, Backyard, Outdoors, Cat, Kitten</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -3798,6 +3798,1156 @@
       <c r="E147" t="inlineStr">
         <is>
           <t>downloaded_images\image_146.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/06/22/16/39/arch-6356637__340.jpg</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Street, Road, Arch, Tower Eiffel Alley,</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>261</v>
+      </c>
+      <c r="D148" t="n">
+        <v>51</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_147.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/21/16/12/blackbird-7083494__340.jpg</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Bird, Worm, Blackbird, Animal, Eating</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>70</v>
+      </c>
+      <c r="D149" t="n">
+        <v>51</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_148.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/10/08/dog-7115247__340.jpg</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Dog, Retriever, Golden Lake Swim, Water,</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>33</v>
+      </c>
+      <c r="D150" t="n">
+        <v>22</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_149.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/21/10/clouds-7122287__340.jpg</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Clouds Sky, Clouds, Grey Atmosphere,</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_150.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/12/12/02/flowers-7127847__340.jpg</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Spring, Seasonal, Bloom Flowers, Nature,</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>17</v>
+      </c>
+      <c r="D152" t="n">
+        <v>14</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_151.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/31/14/12/flower-7103109__340.jpg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Liverflower, Flower, Bloomer Early</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>74</v>
+      </c>
+      <c r="D153" t="n">
+        <v>57</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_152.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/05/29/17/35/car-6293917__340.jpg</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Desktop Car, Wallpaper Sunset, Beach,</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>37</v>
+      </c>
+      <c r="D154" t="n">
+        <v>7</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_153.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/10/23/03/35/mountain-6734031__340.jpg</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Summit, Mountain, Snow, Winter</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>85</v>
+      </c>
+      <c r="D155" t="n">
+        <v>20</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_154.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/11/47/daffodil-7119341__340.jpg</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>am Aufgenommen 5.3.2022</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>29</v>
+      </c>
+      <c r="D156" t="n">
+        <v>22</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_155.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/08/29/08/49/petit-minou-lighthouse-6582717__340.jpg</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Sea Minou Lighthouse, Petit</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>120</v>
+      </c>
+      <c r="D157" t="n">
+        <v>29</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_156.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2018/01/30/22/50/forest-3119826__480.jpg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Forest, Trees, Twilight, Nature, Woods</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D158" t="n">
+        <v>188</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_157.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/07/17/32/european-shorthair-7118037__340.jpg</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Animal Pet, Cat, European Shorthair,</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>18</v>
+      </c>
+      <c r="D159" t="n">
+        <v>8</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_158.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/11/19/35/easter-bunny-7126487__340.jpg</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Festival Easter, Easter Bunny,</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>9</v>
+      </c>
+      <c r="D160" t="n">
+        <v>7</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_159.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/28/17/19/mountains-7097981__340.jpg</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Mountains, Cabin, Clouds, Herb Meadow,</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>63</v>
+      </c>
+      <c r="D161" t="n">
+        <v>55</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_160.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/07/27/16/23/buildings-6497337__340.jpg</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sunset Buildings, Hills, Road, Town,</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>132</v>
+      </c>
+      <c r="D162" t="n">
+        <v>19</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_161.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/14/20/54/city-7069010__340.jpg</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>City Mexico Tourism, Travel, City,</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>19</v>
+      </c>
+      <c r="D163" t="n">
+        <v>5</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_162.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/09/29/magnolia-7121115__340.jpg</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Tree, Spring Magnolia, Flowers Flower,</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_163.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/10/19/17/donkey-7124096__340.jpg</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Animal, Donkey, Draft Mammal</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>10</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_164.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/11/46/weave-7119337__340.jpg</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>am Aufgenommen 20.3.2021</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>27</v>
+      </c>
+      <c r="D166" t="n">
+        <v>19</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_165.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/14/54/fields-7121593__340.jpg</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Fields, Rural Meadow, Nature, Landscape,</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>14</v>
+      </c>
+      <c r="D167" t="n">
+        <v>12</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_166.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/08/13/45/flowers-7119514__340.jpg</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>the This heard Have “hanami”? is ever sit season under you eat Cherry blossoms in now our of cherry for friends. trees and Japan. We with drink</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>14</v>
+      </c>
+      <c r="D168" t="n">
+        <v>8</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_167.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/19/08/45/alley-7078098__340.jpg</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>In kleinen einem Städtchen ...</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>57</v>
+      </c>
+      <c r="D169" t="n">
+        <v>33</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_168.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/06/30/drake-7114868__340.jpg</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Wings Drake, Waterbird,</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>20</v>
+      </c>
+      <c r="D170" t="n">
+        <v>19</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_169.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/11/17/10/57/pine-cone-6803226__340.jpg</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Green, Cone, Fir Branch Pine</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>126</v>
+      </c>
+      <c r="D171" t="n">
+        <v>43</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_170.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/10/15/22/59/heron-6713611__340.jpg</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Lake, Egret, Great Pond River, Heron,</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>163</v>
+      </c>
+      <c r="D172" t="n">
+        <v>127</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_171.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/10/08/06/45/seagulls-6690361__340.jpg</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Sky Birds, Sea, Ocean, Seagulls, Nature,</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>121</v>
+      </c>
+      <c r="D173" t="n">
+        <v>30</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_172.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/07/22/21/55/mountains-6486093__480.jpg</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Mountains, Alpine Hike, Tourism, Nature,</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>122</v>
+      </c>
+      <c r="D174" t="n">
+        <v>24</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_173.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/04/08/43/road-7110643__340.jpg</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Road, Landscape Mountain, Countryside,</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>29</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_174.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/11/11/16/29/tree-6786654__340.jpg</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Season, Tree, Leaves, Autumn, Nature</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>89</v>
+      </c>
+      <c r="D176" t="n">
+        <v>21</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_175.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/23/17/41/fantasy-7087606__340.jpg</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Bird Elf, Light, Magic Fantasy, Plants,</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>32</v>
+      </c>
+      <c r="D177" t="n">
+        <v>17</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_176.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/12/09/27/couple-7063784__340.jpg</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Couple, Meadow, Sunset Nature, Walking,</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>17</v>
+      </c>
+      <c r="D178" t="n">
+        <v>5</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_177.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2016/12/16/15/25/christmas-1911637__340.jpg</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Lay Christmas, Background, Flat</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2860</v>
+      </c>
+      <c r="D179" t="n">
+        <v>460</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_178.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/17/40/blackthorn-7116000__340.jpg</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Prunus Blackthorn, Spinosa Winter, Sloe,</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>23</v>
+      </c>
+      <c r="D180" t="n">
+        <v>20</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_179.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/08/27/19/55/boat-6579441__340.jpg</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Forest, Boat, River, Landscape, Woods</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>145</v>
+      </c>
+      <c r="D181" t="n">
+        <v>26</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_180.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/18/25/walnuts-7122043__340.jpg</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Nuts, Walnuts, Healthy, Food, Nutrition</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>11</v>
+      </c>
+      <c r="D182" t="n">
+        <v>5</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_181.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/12/04/46/climate-change-7127153__340.jpg</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Protest, Change, Climate People</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>12</v>
+      </c>
+      <c r="D183" t="n">
+        <v>9</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_182.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/08/08/15/45/mountains-6531264__340.jpg</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Mountains, Fortress Sunset, Germany,</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>116</v>
+      </c>
+      <c r="D184" t="n">
+        <v>26</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_183.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/11/27/18/28/candles-6828695__340.jpg</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Candlelight, Candles, Christmas</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>122</v>
+      </c>
+      <c r="D185" t="n">
+        <v>60</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_184.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/02/19/08/48/flower-7022112__340.jpg</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Spring Flower, Butterfly, Fantasy,</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>97</v>
+      </c>
+      <c r="D186" t="n">
+        <v>72</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_185.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/04/10/39/australian-wood-duck-7110865__340.jpg</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Wood Australian Duck, Bird</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>45</v>
+      </c>
+      <c r="D187" t="n">
+        <v>44</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_186.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/10/04/16/42/dog-6680642__340.jpg</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Dog, Animal Pet, Doggy, Cute, Puppy,</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>89</v>
+      </c>
+      <c r="D188" t="n">
+        <v>16</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_187.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/31/05/07/cherry-blossom-7102224__340.jpg</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Spring, Blossom, Cherry Flowers Nature,</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>57</v>
+      </c>
+      <c r="D189" t="n">
+        <v>48</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_188.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/26/19/36/christmas-tree-6895765__480.jpg</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Holiday, Season Christmas Tree,</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>54</v>
+      </c>
+      <c r="D190" t="n">
+        <v>11</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_189.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/07/26/22/04/sea-shell-6495338__340.jpg</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sea Shell, Conch Giant</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>206</v>
+      </c>
+      <c r="D191" t="n">
+        <v>95</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_190.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/02/05/18/05/paper-5985445__340.jpg</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Crumpled, Paper, Fold Shadows, Texture,</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>186</v>
+      </c>
+      <c r="D192" t="n">
+        <v>38</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_191.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/03/31/14/16/bee-7103114__340.jpg</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Bee, Pollination, Entomology, Macro</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>57</v>
+      </c>
+      <c r="D193" t="n">
+        <v>41</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_192.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/05/26/butterfly-7114816__340.jpg</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Meadow Aurora Butterfly,</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>25</v>
+      </c>
+      <c r="D194" t="n">
+        <v>16</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_193.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2021/12/02/13/02/candles-6840499__340.jpg</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Weihnachtskerzen 4</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>70</v>
+      </c>
+      <c r="D195" t="n">
+        <v>24</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_194.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/06/14/27/mute-swan-7115661__340.jpg</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>description a (optional) Add</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>40</v>
+      </c>
+      <c r="D196" t="n">
+        <v>33</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_195.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>https://cdn.pixabay.com/photo/2022/04/09/06/20/tulip-7120843__340.jpg</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Flowering, Spring, Flower Tulip,</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>9</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>downloaded_images\image_196.jpg</t>
         </is>
       </c>
     </row>

--- a/stock_images_data.xlsx
+++ b/stock_images_data.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sky, Sky Clouds, Blue Atmosphere,</t>
+          <t>Clouds, Blue Sky, Atmosphere, Sky</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Subtropical Rainbow, Rainfall, Sea,</t>
+          <t>Subtropical Rainfall, Rainbow, Sea,</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -520,7 +520,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Road, Sakura Japan, Cherry Blossoms,</t>
+          <t>Blossoms, Cherry Road, Sakura Japan,</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marguerite, Cape Plant Flower,</t>
+          <t>Plant Flower, Marguerite, Cape</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tree Relaxing Under Rest The</t>
+          <t>Relaxing The Under Rest Tree</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -589,7 +589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rabbit, Cottontail Wild Grass</t>
+          <t>Cottontail Wild Rabbit, Grass</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -612,7 +612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crocus, Flowers, Plant Spring,</t>
+          <t>Plant Spring, Crocus, Flowers,</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Drink, Coffee, Vacation, Café, Table</t>
+          <t>Coffee, Drink, Café, Vacation, Table</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fall, Epic, Nature, Light Waterfall,</t>
+          <t>Waterfall, Fall, Light Nature, Epic,</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nature Field, Sunrise, Dawn, Morning,</t>
+          <t>Dawn, Field, Morning, Sunrise, Nature</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robin, Birdwatching, Bird, Animal</t>
+          <t>Animal Robin, Birdwatching, Bird,</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spring Soil, Bloom Flowers, Seedlings,</t>
+          <t>Spring Bloom Soil, Flowers, Seedlings,</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hills Road, Countryside, Highway,</t>
+          <t>Road, Hills Countryside, Highway,</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Monochrome, Cityscape, City Bridge,</t>
+          <t>Cityscape, City Bridge, Monochrome,</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Water Spring, Sakura, Cherry Blossoms,</t>
+          <t>Sakura, Cherry Blossoms, Water Spring,</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eggs, Template, Background, Art Easter,</t>
+          <t>Background, Art Template, Easter, Eggs,</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Indian Species Ornithology, Chat, Bird,</t>
+          <t>Species Chat, Ornithology, Bird, Indian</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Night, Village, Winter, Season Town,</t>
+          <t>Season Night, Village, Town, Winter,</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bloom Flower, Pansy, Viola, Blossom,</t>
+          <t>Blossom, Flower, Bloom Viola, Pansy,</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Architecture, Lake, Port, Vacations</t>
+          <t>Port, Architecture, Vacations Lake,</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -934,7 +934,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Flowers, Sunflowers, Plant</t>
+          <t>Sunflowers, Flowers, Plant</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spring, Coffee, Flowers, Morning</t>
+          <t>Coffee, Morning Flowers, Spring,</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lake, Peak, Roys Mountains Wanaka,</t>
+          <t>Mountains Wanaka, Roys Lake, Peak,</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thank many downloads and you, likes. for everyone. you</t>
+          <t>Thank and everyone. many downloads you, likes. for you</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Exploration Beach, Outdoors, Nature,</t>
+          <t>Beach, Outdoors, Exploration Nature,</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>West Danish Jutland. during Shot Coast of sunset. The</t>
+          <t>Jutland. during Shot sunset. The of West Danish Coast</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bird, Penguin, Animal Gentoo</t>
+          <t>Animal Gentoo Penguin, Bird,</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sea, Water, Tree Lantern, Heaven, Beach,</t>
+          <t>Water, Lantern, Heaven, Sea, Beach, Tree</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spring, Easter, Easter Bunny</t>
+          <t>Easter, Easter Spring, Bunny</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>on green rock during brown lake daytime trees formation</t>
+          <t>during brown trees green formation on lake rock daytime</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tower, Eiffel Tourist Attraction, Travel</t>
+          <t>Attraction, Tower, Tourist Eiffel Travel</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Standing Stones, Menhir, Clouds, Stones</t>
+          <t>Clouds, Standing Stones Stones, Menhir,</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Path Road, Winter, Snow, Trees, Frost,</t>
+          <t>Road, Snow, Trees, Path Winter, Frost,</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bird, Woodpecker</t>
+          <t>Woodpecker Bird,</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tape, Cassette, Classic Retro, Music,</t>
+          <t>Retro, Classic Tape, Cassette, Music,</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Power Energy, Clouds, Wind Mills,</t>
+          <t>Clouds, Power Mills, Wind Energy,</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tartini, Travel, Square, Tourism, Piran</t>
+          <t>Tourism, Square, Tartini, Piran Travel,</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eggs, Nest, Colored Eggs Easter</t>
+          <t>Nest, Eggs Colored Easter Eggs,</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nature, Winter, Season, Travel Outdoors,</t>
+          <t>Outdoors, Season, Nature, Winter, Travel</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Glacier, Dying Glacier Glaciers, Melting</t>
+          <t>Glaciers, Glacier Glacier, Dying Melting</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jungle, Nature Tropical, Green, Forest,</t>
+          <t>Forest, Green, Jungle, Tropical, Nature</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Flower, Tulip, Petals Bloom, Blossom,</t>
+          <t>Blossom, Petals Flower, Bloom, Tulip,</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Flowers, Petals Pink</t>
+          <t>Pink Flowers, Petals</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Passiflora, Flower, Passion Flower</t>
+          <t>Flower Flower, Passion Passiflora,</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blessing Faith, Prayer, Hope, Religion,</t>
+          <t>Religion, Hope, Faith, Prayer, Blessing</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Star, Cosmos Space, Universe, Galaxy,</t>
+          <t>Star, Universe, Galaxy, Cosmos Space,</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Macro Insect, Dragonfly, Nature,</t>
+          <t>Dragonfly, Insect, Macro Nature,</t>
         </is>
       </c>
       <c r="C49" t="n">
